--- a/Modulo 2 - SQL/Progettazione concettuale.xlsx
+++ b/Modulo 2 - SQL/Progettazione concettuale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bbcc35c869531aa5/Escritorio/Data Analyst/Settimana 5-SQL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="8_{E122181B-FBE2-4FE1-8D8B-57C931B907C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C18D1626-2952-4801-9A28-E1C59297C808}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="8_{E122181B-FBE2-4FE1-8D8B-57C931B907C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6D24A7-AAB4-46B6-9FDD-40D8C9FEFD84}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{514B785D-7F05-4575-86E3-13348F6E6363}"/>
+    <workbookView xWindow="-23148" yWindow="-732" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{514B785D-7F05-4575-86E3-13348F6E6363}"/>
   </bookViews>
   <sheets>
     <sheet name="Grafico_Iniziale" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,18 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={787A2ACE-F7C9-418B-AE7F-852EECDE5782}</author>
+    <author>tc={60AC3A98-D673-4002-B9CB-072F024BD57A}</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{787A2ACE-F7C9-418B-AE7F-852EECDE5782}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{787A2ACE-F7C9-418B-AE7F-852EECDE5782}">
+      <text>
+        <t>[Commento in thread]
+La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
+Commento:
+Tabella debole (si trova nel centro, a le relazioni)</t>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="1" shapeId="0" xr:uid="{60AC3A98-D673-4002-B9CB-072F024BD57A}">
       <text>
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
@@ -58,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="52">
   <si>
     <t xml:space="preserve">Gestione Ordine Fiorentini </t>
   </si>
@@ -187,13 +196,40 @@
   </si>
   <si>
     <t xml:space="preserve">Tabella forte </t>
+  </si>
+  <si>
+    <t>Spedizione</t>
+  </si>
+  <si>
+    <t>SpedizioneID</t>
+  </si>
+  <si>
+    <t>Data_Consegna</t>
+  </si>
+  <si>
+    <t>Trasporto</t>
+  </si>
+  <si>
+    <t>Stato</t>
+  </si>
+  <si>
+    <t>Tracking</t>
+  </si>
+  <si>
+    <t>Peso_Totale</t>
+  </si>
+  <si>
+    <t>Graffico con 3 entità</t>
+  </si>
+  <si>
+    <t>Graffico con 4 entità</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +243,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -268,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -289,7 +331,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,10 +343,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -427,8 +472,8 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>182867</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>453800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -472,7 +517,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>427696</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>61410</xdr:rowOff>
+      <xdr:rowOff>61411</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -512,16 +557,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9538</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>262890</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161938</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>267652</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>324802</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>91693</xdr:rowOff>
+      <xdr:rowOff>63118</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -544,8 +589,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4770120" y="192418"/>
-          <a:ext cx="9205912" cy="2459595"/>
+          <a:off x="5873115" y="161938"/>
+          <a:ext cx="9205912" cy="2434830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>328639</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>67055</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Immagine 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{790A0A82-5A77-AABB-CAA8-94837443BA24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5857875" y="2698806"/>
+          <a:ext cx="8615389" cy="3340424"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -880,7 +969,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D4" dT="2026-05-19T20:20:41.37" personId="{74B2A71C-9D92-4041-BFC4-6606714B7C74}" id="{787A2ACE-F7C9-418B-AE7F-852EECDE5782}">
+  <threadedComment ref="D6" dT="2026-05-19T20:20:41.37" personId="{74B2A71C-9D92-4041-BFC4-6606714B7C74}" id="{787A2ACE-F7C9-418B-AE7F-852EECDE5782}">
+    <text>Tabella debole (si trova nel centro, a le relazioni)</text>
+  </threadedComment>
+  <threadedComment ref="D20" dT="2026-05-19T20:20:41.37" personId="{74B2A71C-9D92-4041-BFC4-6606714B7C74}" id="{60AC3A98-D673-4002-B9CB-072F024BD57A}">
     <text>Tabella debole (si trova nel centro, a le relazioni)</text>
   </threadedComment>
 </ThreadedComments>
@@ -915,67 +1007,67 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>19</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1065,124 +1157,273 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51335EF5-964B-4EEB-9A2E-05FE5F6B54F0}">
-  <dimension ref="B2:I11"/>
+  <dimension ref="B2:G27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="3" t="s">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="3" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="6" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="5"/>
-      <c r="D10" s="3" t="s">
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="5"/>
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="5"/>
-      <c r="D11" s="6" t="s">
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="5"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C26" s="6"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C2:E2"/>
+  <mergeCells count="2">
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
